--- a/diseases/d105/1995-1999.xlsx
+++ b/diseases/d105/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>5</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>11</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>7</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>6</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>15</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>8</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>12</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>3</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>13</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>10</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>7</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>9</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>13</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>11</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>15</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>6</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>19</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>4</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>15</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>7</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>9</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>6</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>9</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>7</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>10</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>1</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>12</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>10</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>2</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>20</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>7</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>12</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>19</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>9</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>13</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>10</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>8</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>19</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>15</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>22</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>13</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>17</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18057,9 +17925,6 @@
       <c r="O90" t="n">
         <v>5</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18450,9 +18315,6 @@
       <c r="O92" t="n">
         <v>16</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18843,9 +18705,6 @@
       <c r="O94" t="n">
         <v>14</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19236,9 +19095,6 @@
       <c r="O96" t="n">
         <v>13</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19629,9 +19485,6 @@
       <c r="O98" t="n">
         <v>10</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20167,9 +20020,6 @@
       <c r="O101" t="n">
         <v>6</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="S101" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20560,9 +20410,6 @@
       <c r="O103" t="n">
         <v>11</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="S103" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20953,9 +20800,6 @@
       <c r="O105" t="n">
         <v>6</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="S105" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21491,9 +21335,6 @@
       <c r="O108" t="n">
         <v>13</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21884,9 +21725,6 @@
       <c r="O110" t="n">
         <v>11</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="S110" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22422,9 +22260,6 @@
       <c r="O113" t="n">
         <v>15</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="S113" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22815,9 +22650,6 @@
       <c r="O115" t="n">
         <v>20</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="S115" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23353,9 +23185,6 @@
       <c r="O118" t="n">
         <v>12</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="S118" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23746,9 +23575,6 @@
       <c r="O120" t="n">
         <v>10</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="S120" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24284,9 +24110,6 @@
       <c r="O123" t="n">
         <v>8</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="S123" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24677,9 +24500,6 @@
       <c r="O125" t="n">
         <v>4</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="S125" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25215,9 +25035,6 @@
       <c r="O128" t="n">
         <v>13</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="S128" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25608,9 +25425,6 @@
       <c r="O130" t="n">
         <v>5</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="S130" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26146,9 +25960,6 @@
       <c r="O133" t="n">
         <v>8</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="S133" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26539,9 +26350,6 @@
       <c r="O135" t="n">
         <v>7</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="S135" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27077,9 +26885,6 @@
       <c r="O138" t="n">
         <v>24</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="S138" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27470,9 +27275,6 @@
       <c r="O140" t="n">
         <v>14</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28008,9 +27810,6 @@
       <c r="O143" t="n">
         <v>24</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="S143" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28401,9 +28200,6 @@
       <c r="O145" t="n">
         <v>7</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="S145" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28939,9 +28735,6 @@
       <c r="O148" t="n">
         <v>21</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="S148" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29332,9 +29125,6 @@
       <c r="O150" t="n">
         <v>4</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="S150" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29870,9 +29660,6 @@
       <c r="O153" t="n">
         <v>14</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="S153" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30263,9 +30050,6 @@
       <c r="O155" t="n">
         <v>7</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="S155" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30801,9 +30585,6 @@
       <c r="O158" t="n">
         <v>8</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31194,9 +30975,6 @@
       <c r="O160" t="n">
         <v>8</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="S160" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31732,9 +31510,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="S163" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32125,9 +31900,6 @@
       <c r="O165" t="n">
         <v>7</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="S165" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32518,9 +32290,6 @@
       <c r="O167" t="n">
         <v>4</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="S167" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33056,9 +32825,6 @@
       <c r="O170" t="n">
         <v>7</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="S170" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33449,9 +33215,6 @@
       <c r="O172" t="n">
         <v>8</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="S172" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33987,9 +33750,6 @@
       <c r="O175" t="n">
         <v>10</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="S175" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34380,9 +34140,6 @@
       <c r="O177" t="n">
         <v>6</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="S177" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34918,9 +34675,6 @@
       <c r="O180" t="n">
         <v>11</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35311,9 +35065,6 @@
       <c r="O182" t="n">
         <v>2</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35849,9 +35600,6 @@
       <c r="O185" t="n">
         <v>10</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="S185" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36242,9 +35990,6 @@
       <c r="O187" t="n">
         <v>5</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="S187" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36780,9 +36525,6 @@
       <c r="O190" t="n">
         <v>8</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="S190" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37173,9 +36915,6 @@
       <c r="O192" t="n">
         <v>6</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="S192" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37711,9 +37450,6 @@
       <c r="O195" t="n">
         <v>16</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="S195" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38104,9 +37840,6 @@
       <c r="O197" t="n">
         <v>13</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="S197" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38642,9 +38375,6 @@
       <c r="O200" t="n">
         <v>27</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="S200" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39035,9 +38765,6 @@
       <c r="O202" t="n">
         <v>13</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="S202" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39573,9 +39300,6 @@
       <c r="O205" t="n">
         <v>20</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39966,9 +39690,6 @@
       <c r="O207" t="n">
         <v>10</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="S207" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40504,9 +40225,6 @@
       <c r="O210" t="n">
         <v>15</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="S210" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40897,9 +40615,6 @@
       <c r="O212" t="n">
         <v>7</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="S212" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41435,9 +41150,6 @@
       <c r="O215" t="n">
         <v>15</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="S215" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41828,9 +41540,6 @@
       <c r="O217" t="n">
         <v>7</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="S217" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42366,9 +42075,6 @@
       <c r="O220" t="n">
         <v>16</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42759,9 +42465,6 @@
       <c r="O222" t="n">
         <v>8</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="S222" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43297,9 +43000,6 @@
       <c r="O225" t="n">
         <v>2</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="S225" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43690,9 +43390,6 @@
       <c r="O227" t="n">
         <v>16</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="S227" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44083,9 +43780,6 @@
       <c r="O229" t="n">
         <v>1</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="S229" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44621,9 +44315,6 @@
       <c r="O232" t="n">
         <v>10</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45014,9 +44705,6 @@
       <c r="O234" t="n">
         <v>4</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="S234" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45552,9 +45240,6 @@
       <c r="O237" t="n">
         <v>14</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45945,9 +45630,6 @@
       <c r="O239" t="n">
         <v>1</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="S239" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46483,9 +46165,6 @@
       <c r="O242" t="n">
         <v>22</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="S242" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46876,9 +46555,6 @@
       <c r="O244" t="n">
         <v>8</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="S244" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47414,9 +47090,6 @@
       <c r="O247" t="n">
         <v>14</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="S247" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47807,9 +47480,6 @@
       <c r="O249" t="n">
         <v>8</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="S249" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48345,9 +48015,6 @@
       <c r="O252" t="n">
         <v>15</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="S252" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48738,9 +48405,6 @@
       <c r="O254" t="n">
         <v>8</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="S254" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49276,9 +48940,6 @@
       <c r="O257" t="n">
         <v>14</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="S257" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49669,9 +49330,6 @@
       <c r="O259" t="n">
         <v>12</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="S259" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50207,9 +49865,6 @@
       <c r="O262" t="n">
         <v>35</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="S262" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50600,9 +50255,6 @@
       <c r="O264" t="n">
         <v>7</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="S264" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51138,9 +50790,6 @@
       <c r="O267" t="n">
         <v>23</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="S267" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51531,9 +51180,6 @@
       <c r="O269" t="n">
         <v>8</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="S269" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52069,9 +51715,6 @@
       <c r="O272" t="n">
         <v>13</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="S272" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52462,9 +52105,6 @@
       <c r="O274" t="n">
         <v>5</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="S274" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -53000,9 +52640,6 @@
       <c r="O277" t="n">
         <v>8</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="S277" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -53393,9 +53030,6 @@
       <c r="O279" t="n">
         <v>3</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="S279" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -53930,9 +53564,6 @@
       </c>
       <c r="O282" t="n">
         <v>14</v>
-      </c>
-      <c r="Q282" t="n">
-        <v>0</v>
       </c>
       <c r="S282" t="inlineStr">
         <is>
